--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0221.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0221.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Dù sao cũng chẳng quan trọng. Điều quan trọng là niềm vui mà {Male=anh ấy;Female=cô ấy} mong muốn mang đến cho mọi người qua vở kịch này. Cậu đồng ý chứ?</t>
+          <t>Dù sao cũng chẳng quan trọng. Điều quan trọng là niềm vui mà {Male=he;Female=she} mong muốn mang đến cho mọi người qua vở kịch này. Cậu đồng ý chứ?</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hê, ta thích việc vừa xem diễn vừa nhâm nhi đồ ăn ngoài trời thế này.</t>
+          <t>Hê, tao thích việc vừa xem diễn vừa nhâm nhi đồ ăn ngoài trời thế này.</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffff&gt;Saved:&lt;/color&gt;: &lt;color=#f7eba6&gt;{0}&lt;/color&gt;&lt;color=#f9ffff&gt;/{1}&lt;/color&gt;</t>
+          <t>&lt;color=#f9ffff&gt;Đã Lưu&lt;/color&gt;: &lt;color=#f7eba6&gt;{0}&lt;/color&gt;&lt;color=#f9ffff&gt;/{1}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả Chính đã hoàn thành thử thách: {0}</t>
+          <t>Resonator Chính đã hoàn thành thử thách: {0}</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>&lt;color=#fde7a1&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Chúng là cá à? Đúng, đúng rồi. Ta nấu xong chưa nhỉ? Chưa, chưa...</t>
+          <t>Chúng là cá à? Đúng, đúng rồi. Tao nấu xong chưa nhỉ? Chưa, chưa...</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Highest Record: {0}</t>
+          <t>Kỷ Lục Cao Nhất: {0}</t>
         </is>
       </c>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Trôi nổi trên dòng nước xiết, ta đã thấy một ánh sáng vàng... Sự uyên bác và thanh nhã của ngươi đã trở thành chân lý mà ta sẽ mãi khắc ghi trong tim.</t>
+          <t>Trôi nổi trên dòng nước xiết, ta đã thấy một ánh sáng vàng... Sự uyên bác và thanh tao của ngươi đã trở thành chân lý mà ta sẽ mãi khắc ghi trong tim.</t>
         </is>
       </c>
     </row>
@@ -22385,7 +22385,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>&lt;color=#5cc35e&gt;Worn Token&lt;/color&gt;</t>
+          <t>&lt;color=#5cc35e&gt;Mảnh Charm Cũ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>&lt;color=#59b4d3&gt;Drifting Token&lt;/color&gt;</t>
+          <t>&lt;color=#59b4d3&gt;Mảnh Phù Hiệu Phiêu Bạt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>&lt;color=#ca6dff&gt;Exquisite Token&lt;/color&gt;</t>
+          <t>&lt;color=#ca6dff&gt;Mã Thông Minh Tinh Xảo&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22580,7 +22580,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffe65a&gt;Mảnh Vàng&lt;/color&gt;</t>
+          <t>&lt;color=#ffe65a&gt;Mảnh Vàng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Suggested Lv. {0}</t>
+          <t>Cấp đề xuất: {0}</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Inferno Rider đang &lt;color=#b72924ff&gt;empowered&lt;/color&gt;.</t>
+          <t>Inferno Rider đang &lt;color=#b72924ff&gt;tràn đầy sức mạnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26545,7 +26545,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Mephis Bão Tố được &lt;color=#b72924ff&gt;empowered&lt;/color&gt; mạnh mẽ.</t>
+          <t>Mephis Bão Tố được &lt;color=#b72924ff&gt;tiếp sức&lt;/color&gt; mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26610,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Rồng Than Khóc: Gehinnom đang được &lt;color=#b72924ff&gt;empowered&lt;/color&gt; mạnh mẽ.</t>
+          <t>Rồng Than Khóc: Gehinnom đang được &lt;color=#b72924ff&gt;tăng cường&lt;/color&gt; mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -26675,7 +26675,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Công Trình Tuần Tra: Gargoyle được &lt;color=#b72924ff&gt;empowered&lt;/color&gt; mạnh mẽ.</t>
+          <t>Công Trình Tuần Tra: Gargoyle được &lt;color=#b72924ff&gt;tăng cường&lt;/color&gt; mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -26740,7 +26740,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả &lt;color=#b72924ff&gt;have their Incoming Healing Bonus reduced by 20%&lt;/color&gt;.</t>
+          <t>Resonator &lt;color=#b72924ff&gt;bị giảm 20% Hiệu Quả Hồi Phục Nhận Vào&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26805,7 +26805,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả &lt;color=#b72924ff&gt;have their Incoming Healing Bonus reduced by 40%&lt;/color&gt;.</t>
+          <t>Resonator &lt;color=#b72924ff&gt;bị giảm 40% Hiệu Quả Hồi Phục Nhận Vào&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Chỉ có thể triển khai Cộng Hưởng Giả sử dụng &lt;color=#b72924ff&gt;Broadblade, Kiếm và Gauntlets&lt;/color&gt;.</t>
+          <t>Chỉ có thể triển khai Resonator sử dụng &lt;color=#b72924ff&gt;Đại kiếm, Kiếm đơn và Găng tay&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Chỉ có thể triển khai Cộng Hưởng Giả sử dụng &lt;color=#b72924ff&gt;Pistols và Rectifier&lt;/color&gt;.</t>
+          <t>Chỉ có thể triển khai Resonator sử dụng &lt;color=#b72924ff&gt;Súng và Pháp khí&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Symphony Rank efficiency is reduced by 25%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;Hiệu suất Cấp Độ Giao Hưởng giảm 25%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27065,7 +27065,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Symphony Rank efficiency is reduced by 50%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;Hiệu suất Cấp Độ Giao Hưởng giảm 50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>&lt;color=#5cc96aff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>&lt;color=#bca868&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Hoàn thành "Thử Thách Tai Họa: Cao Nguyên Desorock" với Mô-đun Áp Lực "Chiến Thuật Đặc Biệt II."</t>
+          <t>Hoàn thành "Thử Thách Tai Họa: Desorock Highland" với Mô-đun Áp Lực "Chiến Thuật Đặc Biệt II."</t>
         </is>
       </c>
     </row>
@@ -27780,7 +27780,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Hoàn thành "Thử Thách Tai Họa: Cao Nguyên Desorock" với Mô-đun Áp Lực "Giấc Mơ Vỡ II."</t>
+          <t>Hoàn thành "Thử Thách Tai Họa: Desorock Highland" với Mô-đun Áp Lực "Giấc Mơ Vỡ II."</t>
         </is>
       </c>
     </row>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Hoàn thành "Thử Thách Tai Họa: Cao Nguyên Desorock" với các Mô-đun Áp Lực "Đẩy Lùi II" và "Rallentando II."</t>
+          <t>Hoàn thành "Thử Thách Tai Họa: Desorock Highland" với các Mô-đun Áp Lực "Đẩy Lùi II" và "Rallentando II."</t>
         </is>
       </c>
     </row>
@@ -28300,7 +28300,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Hoàn thành "Thử Thách Tai Họa: Cao Nguyên Desorock" với các Mô-đun Áp Lực "Khiên Chắn II" và "Bảo Vệ Mở Rộng."</t>
+          <t>Hoàn thành "Thử Thách Tai Họa: Desorock Highland" với các Mô-đun Áp Lực "Khiên Chắn II" và "Bảo Vệ Mở Rộng."</t>
         </is>
       </c>
     </row>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Cấp Độ Căng Thẳng 4 trong Thử Thách Khủng Hoảng: Hàm Hổ.</t>
+          <t>Hoàn thành thử thách với Cấp Độ Căng Thẳng 4 trong Thử Thách Khủng Hoảng: Tiger's Maw.</t>
         </is>
       </c>
     </row>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Cấp Độ Căng Thẳng 4 trong Thử Thách Khủng Hoảng: Đầm Lầy Whining Aix.</t>
+          <t>Hoàn thành thử thách với Cấp Độ Căng Thẳng 4 trong Thử Thách Khủng Hoảng: Whining Aix's Mire.</t>
         </is>
       </c>
     </row>
@@ -29015,7 +29015,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với Cấp Độ Căng Thẳng 4 trong Thử Thách Khủng Hoảng: Núi Firmament.</t>
+          <t>Hoàn thành thử thách với Cấp Độ Căng Thẳng 4 trong Thử Thách Khủng Hoảng: Mt. Firmament.</t>
         </is>
       </c>
     </row>
